--- a/outputs/preprocessing/pca_loadings_all_features.xlsx
+++ b/outputs/preprocessing/pca_loadings_all_features.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trish\Downloads\Predicting-Number-of-Hospitals\outputs\preprocessing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646A5133-D4A3-44C0-AAE3-1097D7A4CCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{774EBC8B-35CD-4849-8F45-9FA0EBD893A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PC Loadings - All Features" sheetId="1" r:id="rId1"/>
@@ -6951,9 +6951,8 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="20" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="41" hidden="1" customWidth="1"/>
+    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="41" customWidth="1"/>
     <col min="4" max="4" width="38.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
